--- a/output/pdf_financials_xlsx/LORD.xlsx
+++ b/output/pdf_financials_xlsx/LORD.xlsx
@@ -5406,49 +5406,49 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.874129</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.016507</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.672991</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.094683</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.082276</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.025444</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.025872</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.04137</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.015424</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.786308</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.40802</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.55432</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.84602</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.84602</v>
       </c>
     </row>
     <row r="93">
@@ -6799,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>5.646307</v>
+        <v>3.306307</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>11.6342</v>
@@ -8844,7 +8844,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10015,7 +10019,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11281,7 +11289,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -12108,7 +12120,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12810,7 +12826,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -13405,7 +13425,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -13852,7 +13876,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>1.874129</v>
       </c>
@@ -23846,7 +23874,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LORD.xlsx
+++ b/output/pdf_financials_xlsx/LORD.xlsx
@@ -990,28 +990,28 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002729</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000414</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000334</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000182</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000146</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000126</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.174115</v>
+        <v>-1.176844</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.544523</v>
+        <v>-0.5445410000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.493038</v>
+        <v>-0.493452</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.383549</v>
+        <v>-0.383883</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.28647</v>
+        <v>-0.286652</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.180749</v>
+        <v>-0.180895</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.151701</v>
+        <v>-0.151855</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.18547</v>
+        <v>-0.185596</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.614658</v>
@@ -1984,28 +1984,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.174115</v>
+        <v>-1.176844</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.544523</v>
+        <v>-0.5445410000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.493038</v>
+        <v>-0.493452</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.383549</v>
+        <v>-0.383883</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.28647</v>
+        <v>-0.286652</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.180749</v>
+        <v>-0.180895</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.151701</v>
+        <v>-0.151855</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.18547</v>
+        <v>-0.185596</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.614658</v>
@@ -2258,49 +2258,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.332585</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.030471</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.007485</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000233</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001709</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.106948</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.024504</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.100435</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.530084</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.211191</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.19389</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.143951</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.033483</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.046162</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.241949</v>
       </c>
     </row>
     <row r="35">
@@ -2362,49 +2362,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.332585</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.030471</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.007485</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000233</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001709</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.106948</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.024504</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.100435</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.530084</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.211191</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.19389</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.143951</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.033483</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.046162</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.241949</v>
       </c>
     </row>
     <row r="37">
@@ -2986,49 +2986,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.353285</v>
+        <v>0.0207</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.053331</v>
+        <v>0.02286</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.027883</v>
+        <v>0.020398</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.008066</v>
+        <v>0.007833</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.01031</v>
+        <v>0.008600999999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.109304</v>
+        <v>0.002356</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.024504</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.100435</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.530084</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.212691</v>
+        <v>0.0015</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.007228</v>
+        <v>0.813338</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.328172</v>
+        <v>0.184221</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.054286</v>
+        <v>0.020803</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.073126</v>
+        <v>0.026964</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.2821</v>
+        <v>0.040151</v>
       </c>
     </row>
     <row r="49">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -37724,7 +37724,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -38343,7 +38343,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -41035,7 +41035,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">

--- a/output/pdf_financials_xlsx/LORD.xlsx
+++ b/output/pdf_financials_xlsx/LORD.xlsx
@@ -3880,19 +3880,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.054962</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.030115</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.067719</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.141541</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.104133</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -4036,49 +4036,49 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.026195</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0195</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.01675</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.37513</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>1.321091</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.426305</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.541376</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.060554</v>
       </c>
     </row>
     <row r="68">
@@ -5854,22 +5854,22 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00216</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.008462000000000001</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004426</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.006245</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>-8.2e-05</v>
+        <v>0.001705</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0</v>
@@ -6124,22 +6124,22 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.015884</v>
+        <v>-0.018044</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.028854</v>
+        <v>0.037316</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.06807199999999999</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.03375</v>
+        <v>-0.038176</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.003496</v>
+        <v>0.002749</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.015436</v>
+        <v>0.017223</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>0.003472</v>
@@ -27981,7 +27981,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -29532,7 +29536,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -29894,7 +29902,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -32175,7 +32187,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
